--- a/output_petroleo_lp_modelo9/resumo_modelo9_primeiro_estagio.xlsx
+++ b/output_petroleo_lp_modelo9/resumo_modelo9_primeiro_estagio.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,7 +492,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
+          <t>output_petroleo_lp_modelo9\resumo_modelo9_primeiro_estagio.csv</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -526,7 +526,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
+          <t>output_petroleo_lp_modelo9\resumo_modelo9_primeiro_estagio.csv</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -560,7 +560,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
+          <t>output_petroleo_lp_modelo9\resumo_modelo9_primeiro_estagio.csv</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -594,7 +594,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
+          <t>output_petroleo_lp_modelo9\resumo_modelo9_primeiro_estagio.csv</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -612,23 +612,23 @@
         <v>266</v>
       </c>
       <c r="C6" t="n">
-        <v>123.4066238634609</v>
+        <v>128.3459611375896</v>
       </c>
       <c r="D6" t="n">
-        <v>3.377142140578943e-23</v>
+        <v>6.79409209403239e-24</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5359005751051477</v>
+        <v>0.5393701814204114</v>
       </c>
       <c r="F6" t="n">
-        <v>1.136088909901773e-28</v>
+        <v>9.428819885456561e-30</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6191028506077115</v>
+        <v>0.6172715035562735</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -646,23 +646,23 @@
         <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>121.8948128838388</v>
+        <v>126.7411545984158</v>
       </c>
       <c r="D7" t="n">
-        <v>6.270318319839454e-23</v>
+        <v>1.300501702804285e-23</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5327896248238395</v>
+        <v>0.5365949664919272</v>
       </c>
       <c r="F7" t="n">
-        <v>2.434067170540309e-28</v>
+        <v>2.116545791562071e-29</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6189633343660863</v>
+        <v>0.6163800051469981</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -680,23 +680,23 @@
         <v>260</v>
       </c>
       <c r="C8" t="n">
-        <v>118.5390115802745</v>
+        <v>123.500833788249</v>
       </c>
       <c r="D8" t="n">
-        <v>2.13071792073898e-22</v>
+        <v>4.222558706905314e-23</v>
       </c>
       <c r="E8" t="n">
-        <v>0.533428937450821</v>
+        <v>0.5379042565614593</v>
       </c>
       <c r="F8" t="n">
-        <v>1.321297482685658e-27</v>
+        <v>1.083407325645877e-28</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6180700356476124</v>
+        <v>0.6164095614385803</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -714,23 +714,23 @@
         <v>254</v>
       </c>
       <c r="C9" t="n">
-        <v>113.8833780360036</v>
+        <v>119.2661330223113</v>
       </c>
       <c r="D9" t="n">
-        <v>1.25758824953858e-21</v>
+        <v>2.157889667953848e-22</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5307269968092512</v>
+        <v>0.5355960219487748</v>
       </c>
       <c r="F9" t="n">
-        <v>1.382023277585363e-26</v>
+        <v>9.15802290787862e-28</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6179031424081775</v>
+        <v>0.6156850543202197</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -748,23 +748,23 @@
         <v>266</v>
       </c>
       <c r="C10" t="n">
-        <v>124.6951308196308</v>
+        <v>123.4066238634609</v>
       </c>
       <c r="D10" t="n">
-        <v>2.217777391640481e-23</v>
+        <v>3.377142140578943e-23</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5364785392479838</v>
+        <v>0.5359005751051477</v>
       </c>
       <c r="F10" t="n">
-        <v>5.934662943025197e-29</v>
+        <v>1.136088909901773e-28</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6171575975722364</v>
+        <v>0.6191028506077115</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -782,23 +782,23 @@
         <v>263</v>
       </c>
       <c r="C11" t="n">
-        <v>123.1874191502729</v>
+        <v>121.8948128838388</v>
       </c>
       <c r="D11" t="n">
-        <v>4.112676417326383e-23</v>
+        <v>6.270318319839454e-23</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5334958074455329</v>
+        <v>0.5327896248238395</v>
       </c>
       <c r="F11" t="n">
-        <v>1.26879673944373e-28</v>
+        <v>2.434067170540309e-28</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6168154929884018</v>
+        <v>0.6189633343660863</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -816,23 +816,23 @@
         <v>260</v>
       </c>
       <c r="C12" t="n">
-        <v>119.8052677097702</v>
+        <v>118.5390115802745</v>
       </c>
       <c r="D12" t="n">
-        <v>1.406509780257039e-22</v>
+        <v>2.13071792073898e-22</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5346164416703589</v>
+        <v>0.533428937450821</v>
       </c>
       <c r="F12" t="n">
-        <v>6.978570469230264e-28</v>
+        <v>1.321297482685658e-27</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6161345311302939</v>
+        <v>0.6180700356476124</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -850,23 +850,23 @@
         <v>254</v>
       </c>
       <c r="C13" t="n">
-        <v>115.1965913828036</v>
+        <v>113.8833780360036</v>
       </c>
       <c r="D13" t="n">
-        <v>8.158436602333592e-22</v>
+        <v>1.25758824953858e-21</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5320994912933085</v>
+        <v>0.5307269968092512</v>
       </c>
       <c r="F13" t="n">
-        <v>7.126999815236759e-27</v>
+        <v>1.382023277585363e-26</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6154547869686233</v>
+        <v>0.6179031424081775</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -884,23 +884,23 @@
         <v>266</v>
       </c>
       <c r="C14" t="n">
-        <v>125.6862316210125</v>
+        <v>124.6951308196308</v>
       </c>
       <c r="D14" t="n">
-        <v>1.606585218056111e-23</v>
+        <v>2.217777391640481e-23</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5370599880143926</v>
+        <v>0.5364785392479838</v>
       </c>
       <c r="F14" t="n">
-        <v>3.601542767805604e-29</v>
+        <v>5.934662943025197e-29</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6142549270361584</v>
+        <v>0.6171575975722364</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -918,23 +918,23 @@
         <v>263</v>
       </c>
       <c r="C15" t="n">
-        <v>124.1501441424754</v>
+        <v>123.1874191502729</v>
       </c>
       <c r="D15" t="n">
-        <v>3.007151488416594e-23</v>
+        <v>4.112676417326383e-23</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5340780085123942</v>
+        <v>0.5334958074455329</v>
       </c>
       <c r="F15" t="n">
-        <v>7.810428064992257e-29</v>
+        <v>1.26879673944373e-28</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6137770771786002</v>
+        <v>0.6168154929884018</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -952,23 +952,23 @@
         <v>260</v>
       </c>
       <c r="C16" t="n">
-        <v>120.6950597786472</v>
+        <v>119.8052677097702</v>
       </c>
       <c r="D16" t="n">
-        <v>1.051469646147658e-22</v>
+        <v>1.406509780257039e-22</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5355474027536222</v>
+        <v>0.5346164416703589</v>
       </c>
       <c r="F16" t="n">
-        <v>4.456249126094109e-28</v>
+        <v>6.978570469230264e-28</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6133342538064643</v>
+        <v>0.6161345311302939</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -986,23 +986,23 @@
         <v>254</v>
       </c>
       <c r="C17" t="n">
-        <v>115.9090079177726</v>
+        <v>115.1965913828036</v>
       </c>
       <c r="D17" t="n">
-        <v>6.456144984636169e-22</v>
+        <v>8.158436602333592e-22</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5332767540246383</v>
+        <v>0.5320994912933085</v>
       </c>
       <c r="F17" t="n">
-        <v>4.97612075962558e-27</v>
+        <v>7.126999815236759e-27</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6128837288880624</v>
+        <v>0.6154547869686233</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1020,23 +1020,23 @@
         <v>266</v>
       </c>
       <c r="C18" t="n">
-        <v>127.3226784720803</v>
+        <v>125.6862316210125</v>
       </c>
       <c r="D18" t="n">
-        <v>9.453559557433268e-24</v>
+        <v>1.606585218056111e-23</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5371999961344709</v>
+        <v>0.5370599880143926</v>
       </c>
       <c r="F18" t="n">
-        <v>1.578964546245356e-29</v>
+        <v>3.601542767805604e-29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6170803661030896</v>
+        <v>0.6142549270361584</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1054,23 +1054,23 @@
         <v>263</v>
       </c>
       <c r="C19" t="n">
-        <v>125.4303813892021</v>
+        <v>124.1501441424754</v>
       </c>
       <c r="D19" t="n">
-        <v>1.985796547639876e-23</v>
+        <v>3.007151488416594e-23</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5339392937229838</v>
+        <v>0.5340780085123942</v>
       </c>
       <c r="F19" t="n">
-        <v>4.097146060479594e-29</v>
+        <v>7.810428064992257e-29</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6174778872438316</v>
+        <v>0.6137770771786002</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1088,23 +1088,23 @@
         <v>260</v>
       </c>
       <c r="C20" t="n">
-        <v>122.8578711897179</v>
+        <v>120.6950597786472</v>
       </c>
       <c r="D20" t="n">
-        <v>5.200933773108416e-23</v>
+        <v>1.051469646147658e-22</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5356796458299189</v>
+        <v>0.5355474027536222</v>
       </c>
       <c r="F20" t="n">
-        <v>1.498045747106857e-28</v>
+        <v>4.456249126094109e-28</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6170970836322504</v>
+        <v>0.6133342538064643</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1122,23 +1122,23 @@
         <v>254</v>
       </c>
       <c r="C21" t="n">
-        <v>118.1142271048735</v>
+        <v>115.9090079177726</v>
       </c>
       <c r="D21" t="n">
-        <v>3.138953543436554e-22</v>
+        <v>6.456144984636169e-22</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5329623275312303</v>
+        <v>0.5332767540246383</v>
       </c>
       <c r="F21" t="n">
-        <v>1.636847718262772e-27</v>
+        <v>4.97612075962558e-27</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6162889776364455</v>
+        <v>0.6128837288880624</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1156,23 +1156,23 @@
         <v>266</v>
       </c>
       <c r="C22" t="n">
-        <v>128.719032927988</v>
+        <v>127.3226784720803</v>
       </c>
       <c r="D22" t="n">
-        <v>6.024644836721237e-24</v>
+        <v>9.453559557433268e-24</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5366822588661285</v>
+        <v>0.5371999961344709</v>
       </c>
       <c r="F22" t="n">
-        <v>7.81312900630757e-30</v>
+        <v>1.578964546245356e-29</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6181740835624511</v>
+        <v>0.6170803661030896</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1190,23 +1190,23 @@
         <v>263</v>
       </c>
       <c r="C23" t="n">
-        <v>126.9954094119917</v>
+        <v>125.4303813892021</v>
       </c>
       <c r="D23" t="n">
-        <v>1.198215792226263e-23</v>
+        <v>1.985796547639876e-23</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5334255912463788</v>
+        <v>0.5339392937229838</v>
       </c>
       <c r="F23" t="n">
-        <v>1.862037232275296e-29</v>
+        <v>4.097146060479594e-29</v>
       </c>
       <c r="G23" t="n">
-        <v>0.618027027930574</v>
+        <v>0.6174778872438316</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1224,23 +1224,23 @@
         <v>260</v>
       </c>
       <c r="C24" t="n">
-        <v>123.2344036952497</v>
+        <v>122.8578711897179</v>
       </c>
       <c r="D24" t="n">
-        <v>4.603184861434509e-23</v>
+        <v>5.200933773108416e-23</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5341994841688877</v>
+        <v>0.5356796458299189</v>
       </c>
       <c r="F24" t="n">
-        <v>1.239104620872225e-28</v>
+        <v>1.498045747106857e-28</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6171463933405273</v>
+        <v>0.6170970836322504</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1258,29 +1258,165 @@
         <v>254</v>
       </c>
       <c r="C25" t="n">
-        <v>118.8751750973308</v>
+        <v>118.1142271048735</v>
       </c>
       <c r="D25" t="n">
-        <v>2.450216510222392e-22</v>
+        <v>3.138953543436554e-22</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5313933731997886</v>
+        <v>0.5329623275312303</v>
       </c>
       <c r="F25" t="n">
-        <v>1.115317823825639e-27</v>
+        <v>1.636847718262772e-27</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6165766613107138</v>
+        <v>0.6162889776364455</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
         </is>
       </c>
       <c r="I25" t="n">
         <v>12</v>
       </c>
       <c r="J25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0</v>
+      </c>
+      <c r="B26" t="n">
+        <v>266</v>
+      </c>
+      <c r="C26" t="n">
+        <v>128.719032927988</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6.024644836721237e-24</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5366822588661285</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7.81312900630757e-30</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.6181740835624511</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" t="n">
+        <v>263</v>
+      </c>
+      <c r="C27" t="n">
+        <v>126.9954094119917</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.198215792226263e-23</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5334255912463788</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.862037232275296e-29</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.618027027930574</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" t="n">
+        <v>260</v>
+      </c>
+      <c r="C28" t="n">
+        <v>123.2344036952497</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4.603184861434509e-23</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5341994841688877</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.239104620872225e-28</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.6171463933405273</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>254</v>
+      </c>
+      <c r="C29" t="n">
+        <v>118.8751750973308</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.450216510222392e-22</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.5313933731997886</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.115317823825639e-27</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.6165766613107138</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\primeiro_estagio_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>12</v>
+      </c>
+      <c r="J29" t="b">
         <v>1</v>
       </c>
     </row>
